--- a/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk32\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IDM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IDM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CC9C30-2145-44F6-84C6-84139B077C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F260ADA5-CC6C-4176-867F-FCE37238150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D801CD60-5F13-429A-8867-9B4185E3A355}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{D801CD60-5F13-429A-8867-9B4185E3A355}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1946,7 +1946,7 @@
         <v>218</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>219</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IDM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F260ADA5-CC6C-4176-867F-FCE37238150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EC7F9C-D788-4462-9313-0B2DDFAFA55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{D801CD60-5F13-429A-8867-9B4185E3A355}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D801CD60-5F13-429A-8867-9B4185E3A355}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="367">
   <si>
     <t>StepNo</t>
   </si>
@@ -1152,6 +1152,9 @@
   </si>
   <si>
     <t>Wait for EPR View to load and get the NHS number</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2386,7 +2389,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="7" t="s">
-        <v>15</v>
+        <v>366</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -3209,7 +3212,7 @@
         <v>88</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>15</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IDM/LSTP_IDM_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IDM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EC7F9C-D788-4462-9313-0B2DDFAFA55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F677448-9B08-47F8-8356-1C118EFA067E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D801CD60-5F13-429A-8867-9B4185E3A355}"/>
   </bookViews>
@@ -3253,7 +3253,7 @@
         <v>294</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>91</v>
